--- a/customers/amir reza.xlsx
+++ b/customers/amir reza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -61,6 +61,12 @@
   </si>
   <si>
     <t>ساندویچ باغ ممد جواد</t>
+  </si>
+  <si>
+    <t>1405/04/24</t>
+  </si>
+  <si>
+    <t>چوب شور</t>
   </si>
 </sst>
 </file>
@@ -495,7 +501,7 @@
       </c>
       <c r="H2" s="9">
         <f>A23</f>
-        <v>333000</v>
+        <v>358000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -548,18 +554,24 @@
     <row r="6" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
-      </c>
-      <c r="B6" s="6"/>
+        <v>358000</v>
+      </c>
+      <c r="B6" s="6">
+        <v>25000</v>
+      </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="3"/>
+      <c r="D6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -570,7 +582,7 @@
     <row r="8" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -581,7 +593,7 @@
     <row r="9" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -592,7 +604,7 @@
     <row r="10" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -603,7 +615,7 @@
     <row r="11" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -614,7 +626,7 @@
     <row r="12" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -625,7 +637,7 @@
     <row r="13" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -636,7 +648,7 @@
     <row r="14" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -647,7 +659,7 @@
     <row r="15" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -658,7 +670,7 @@
     <row r="16" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -669,7 +681,7 @@
     <row r="17" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -680,7 +692,7 @@
     <row r="18" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -691,7 +703,7 @@
     <row r="19" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -702,7 +714,7 @@
     <row r="20" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -713,7 +725,7 @@
     <row r="21" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <f t="shared" si="0"/>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -725,7 +737,7 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7">
         <f>SUM(B3:B21)</f>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="C22" s="7">
         <f>SUM(C3:C21)</f>
@@ -738,7 +750,7 @@
     <row r="23" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <f>A21</f>
-        <v>333000</v>
+        <v>358000</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="10" t="s">

--- a/customers/amir reza.xlsx
+++ b/customers/amir reza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>چوب شور</t>
+  </si>
+  <si>
+    <t>سیگار</t>
   </si>
 </sst>
 </file>
@@ -501,7 +504,7 @@
       </c>
       <c r="H2" s="9">
         <f>A23</f>
-        <v>358000</v>
+        <v>366000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -571,18 +574,22 @@
     <row r="7" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
-      </c>
-      <c r="B7" s="6"/>
+        <v>366000</v>
+      </c>
+      <c r="B7" s="6">
+        <v>8000</v>
+      </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -593,7 +600,7 @@
     <row r="9" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -604,7 +611,7 @@
     <row r="10" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -615,7 +622,7 @@
     <row r="11" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -626,7 +633,7 @@
     <row r="12" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -637,7 +644,7 @@
     <row r="13" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -648,7 +655,7 @@
     <row r="14" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -659,7 +666,7 @@
     <row r="15" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -670,7 +677,7 @@
     <row r="16" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -681,7 +688,7 @@
     <row r="17" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -692,7 +699,7 @@
     <row r="18" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -703,7 +710,7 @@
     <row r="19" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -714,7 +721,7 @@
     <row r="20" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -725,7 +732,7 @@
     <row r="21" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <f t="shared" si="0"/>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -737,7 +744,7 @@
       <c r="A22" s="7"/>
       <c r="B22" s="7">
         <f>SUM(B3:B21)</f>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="C22" s="7">
         <f>SUM(C3:C21)</f>
@@ -750,7 +757,7 @@
     <row r="23" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <f>A21</f>
-        <v>358000</v>
+        <v>366000</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="10" t="s">
